--- a/outputs/daily/hr_rankings_2026-10-12_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-12_remaining.xlsx
@@ -735,27 +735,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>660271</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Shohei Ohtani</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -765,26 +765,26 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>59.4</v>
+        <v>51.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,26 +798,26 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>79.3</v>
+        <v>62</v>
       </c>
       <c r="Q2" t="n">
-        <v>36.5</v>
+        <v>21.5</v>
       </c>
       <c r="R2" t="n">
         <v>27.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U2" t="n">
-        <v>8.800000000000001</v>
+        <v>37.8</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -873,134 +873,134 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>54.08</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>93.78</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>104.473</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.5811</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.2987</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.4054</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>75.03</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>52.87</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>31.92</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.2679</t>
+          <t>0.2549</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr"/>
@@ -1011,27 +1011,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1041,17 +1041,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>52.2</v>
+        <v>48.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,26 +1074,26 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>51.1</v>
+        <v>53.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>36.5</v>
+        <v>33.4</v>
       </c>
       <c r="R3" t="n">
         <v>27.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
       </c>
       <c r="U3" t="n">
-        <v>100</v>
+        <v>34.9</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1149,134 +1149,134 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>90.79</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>103.0119</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.4755</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.2176</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>69.77</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>72.74</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.1874</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr"/>
@@ -1287,27 +1287,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>800050</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1317,17 +1317,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.9</v>
+        <v>46.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,26 +1350,26 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>59.6</v>
+        <v>35.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>26.6</v>
+        <v>33.4</v>
       </c>
       <c r="R4" t="n">
         <v>27.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>16.6</v>
+        <v>56.2</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -1425,27 +1425,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1455,104 +1455,104 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>102.9654</t>
+          <t>101.3425</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.427</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.149</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3659</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>69.02</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr"/>
@@ -1563,27 +1563,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1598,21 +1598,21 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>47.1</v>
+        <v>44.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,14 +1626,14 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>39.3</v>
+        <v>48.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>36.5</v>
+        <v>21.5</v>
       </c>
       <c r="R5" t="n">
         <v>27.6</v>
@@ -1642,10 +1642,10 @@
         <v>95.5</v>
       </c>
       <c r="T5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>13</v>
+        <v>28.9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1701,134 +1701,134 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr"/>
@@ -1839,27 +1839,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1869,17 +1869,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>47.1</v>
+        <v>43.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,26 +1902,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>50.1</v>
+        <v>36.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>26.6</v>
+        <v>33.4</v>
       </c>
       <c r="R6" t="n">
         <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>63.3</v>
+        <v>10.1</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1977,27 +1977,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2007,104 +2007,104 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1951</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr"/>
@@ -2115,27 +2115,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2145,26 +2145,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.4</v>
+        <v>43.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>45.7</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="n">
-        <v>36.5</v>
+        <v>21.5</v>
       </c>
       <c r="R7" t="n">
         <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U7" t="n">
-        <v>48.3</v>
+        <v>20.9</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2253,134 +2253,134 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr"/>
@@ -2391,27 +2391,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2421,26 +2421,26 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.4</v>
+        <v>43.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2458,22 +2458,22 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36.6</v>
+        <v>43.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>26.6</v>
+        <v>21.5</v>
       </c>
       <c r="R8" t="n">
         <v>27.6</v>
       </c>
       <c r="S8" t="n">
-        <v>95.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U8" t="n">
-        <v>65.2</v>
+        <v>0</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2529,27 +2529,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2559,104 +2559,104 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr"/>
       <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr"/>
@@ -2667,27 +2667,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Victor Mesa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2697,26 +2697,26 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44</v>
+        <v>42.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,26 +2730,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>47.1</v>
+        <v>43.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.6</v>
+        <v>21.5</v>
       </c>
       <c r="R9" t="n">
         <v>27.6</v>
       </c>
       <c r="S9" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>13.3</v>
+        <v>54.9</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2805,134 +2805,134 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr"/>
       <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr"/>
@@ -2943,27 +2943,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2973,17 +2973,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>42.8</v>
+        <v>41.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,26 +3006,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>39.5</v>
+        <v>25.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>26.6</v>
+        <v>31.6</v>
       </c>
       <c r="R10" t="n">
         <v>27.6</v>
       </c>
       <c r="S10" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T10" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U10" t="n">
-        <v>37.8</v>
+        <v>23.4</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -3081,27 +3081,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3111,104 +3111,104 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr"/>
       <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr"/>
@@ -3219,27 +3219,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3249,17 +3249,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>42.1</v>
+        <v>40</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,26 +3282,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>32.7</v>
+        <v>32.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>36.5</v>
+        <v>31.6</v>
       </c>
       <c r="R11" t="n">
         <v>27.6</v>
       </c>
       <c r="S11" t="n">
-        <v>88.7</v>
+        <v>59.8</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U11" t="n">
-        <v>29.2</v>
+        <v>48.7</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -3357,134 +3357,134 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>99.7502</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr"/>
       <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr"/>
@@ -3495,27 +3495,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>41.1</v>
+        <v>36.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,26 +3558,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>36.4</v>
+        <v>20.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>36.5</v>
+        <v>33.4</v>
       </c>
       <c r="R12" t="n">
         <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T12" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3633,134 +3633,134 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>99.6965</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4378</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -3771,27 +3771,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3801,17 +3801,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>40.3</v>
+        <v>34.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,26 +3834,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>35.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>36.5</v>
+        <v>33.4</v>
       </c>
       <c r="R13" t="n">
         <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>88.7</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>26.1</v>
+        <v>43.1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -3924,119 +3924,119 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>100.9708</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3621</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>43.52</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.51</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1594</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr"/>
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr"/>
@@ -4047,27 +4047,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4077,26 +4077,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>38.6</v>
+        <v>33.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,26 +4110,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>33.9</v>
+        <v>10.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>36.5</v>
+        <v>21.5</v>
       </c>
       <c r="R14" t="n">
         <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U14" t="n">
-        <v>12</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4185,134 +4185,134 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.7109</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>27.96</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -4323,27 +4323,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>683734</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Andrew Vaughn</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4353,17 +4353,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>38.4</v>
+        <v>32.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,26 +4386,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>34.2</v>
+        <v>13.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>26.6</v>
+        <v>31.6</v>
       </c>
       <c r="R15" t="n">
         <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>81.90000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>13.6</v>
+        <v>72.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -4461,27 +4461,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4491,104 +4491,104 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>44.76</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>90.55</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>100.1817</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4097</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>70.53</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>12.73</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>33.72</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1437</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -4599,27 +4599,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>571771</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Enrique Hernandez</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4629,17 +4629,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>35.2</v>
+        <v>30.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,26 +4662,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>32.6</v>
+        <v>7.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>36.5</v>
+        <v>33.4</v>
       </c>
       <c r="R16" t="n">
         <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>28.5</v>
+        <v>38.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4742,129 +4742,129 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 1 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>39.49</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.9102</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3751</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1548</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2814</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.82</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1735</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr"/>
       <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -4875,27 +4875,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4905,26 +4905,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.3</v>
+        <v>28.5</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4942,22 +4942,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>16.6</v>
+        <v>11.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>24.6</v>
+        <v>21.5</v>
       </c>
       <c r="R17" t="n">
         <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U17" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -5013,12 +5013,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5028,12 +5028,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5043,104 +5043,104 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -5151,27 +5151,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>663743</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -5181,26 +5181,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>28.1</v>
+        <v>27.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,26 +5214,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>10.5</v>
+        <v>12.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>26.6</v>
+        <v>21.5</v>
       </c>
       <c r="R18" t="n">
         <v>27.6</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U18" t="n">
-        <v>24.9</v>
+        <v>18.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5289,27 +5289,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 2/17, 1 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5319,104 +5319,104 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.03</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>99.0812</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3248</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.093</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2721</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>72.49</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr"/>
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr"/>
@@ -5427,27 +5427,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -5457,26 +5457,26 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>27.4</v>
+        <v>25.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,26 +5490,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>17.1</v>
+        <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>26.6</v>
+        <v>20.1</v>
       </c>
       <c r="R19" t="n">
         <v>27.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T19" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>22.4</v>
+        <v>27</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -5565,12 +5565,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5595,104 +5595,104 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>95.5424</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0794</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.35</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.0829</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr"/>
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr"/>
@@ -6029,27 +6029,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>660271</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Shohei Ohtani</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6059,26 +6059,26 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>59.4</v>
+        <v>51.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6092,26 +6092,26 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>79.3</v>
+        <v>62</v>
       </c>
       <c r="Q2" t="n">
-        <v>36.5</v>
+        <v>21.5</v>
       </c>
       <c r="R2" t="n">
         <v>27.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U2" t="n">
-        <v>8.800000000000001</v>
+        <v>37.8</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -6167,134 +6167,134 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>54.08</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>93.78</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>104.473</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.5811</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.2987</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.4054</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>75.03</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>52.87</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>31.92</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.2679</t>
+          <t>0.2549</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr"/>
@@ -6305,27 +6305,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6335,17 +6335,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -6354,7 +6354,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>52.2</v>
+        <v>48.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,26 +6368,26 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>51.1</v>
+        <v>53.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>36.5</v>
+        <v>33.4</v>
       </c>
       <c r="R3" t="n">
         <v>27.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
       </c>
       <c r="U3" t="n">
-        <v>100</v>
+        <v>34.9</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -6443,134 +6443,134 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>90.79</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>103.0119</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.4755</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.2176</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>69.77</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>72.74</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.1874</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr"/>
@@ -6581,27 +6581,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>800050</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6611,17 +6611,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -6630,7 +6630,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.9</v>
+        <v>46.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,26 +6644,26 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>59.6</v>
+        <v>35.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>26.6</v>
+        <v>33.4</v>
       </c>
       <c r="R4" t="n">
         <v>27.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>16.6</v>
+        <v>56.2</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -6719,27 +6719,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -6749,104 +6749,104 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>102.9654</t>
+          <t>101.3425</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.427</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.149</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3659</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>69.02</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr"/>
@@ -6857,27 +6857,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6892,21 +6892,21 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>47.1</v>
+        <v>44.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,14 +6920,14 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>39.3</v>
+        <v>48.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>36.5</v>
+        <v>21.5</v>
       </c>
       <c r="R5" t="n">
         <v>27.6</v>
@@ -6936,10 +6936,10 @@
         <v>95.5</v>
       </c>
       <c r="T5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>13</v>
+        <v>28.9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -6995,134 +6995,134 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr"/>
@@ -7133,27 +7133,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -7163,17 +7163,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -7182,7 +7182,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>47.1</v>
+        <v>43.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,26 +7196,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>50.1</v>
+        <v>36.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>26.6</v>
+        <v>33.4</v>
       </c>
       <c r="R6" t="n">
         <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>63.3</v>
+        <v>10.1</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -7271,27 +7271,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -7301,104 +7301,104 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1951</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr"/>
@@ -7409,27 +7409,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -7439,26 +7439,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.4</v>
+        <v>43.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,26 +7472,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>45.7</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="n">
-        <v>36.5</v>
+        <v>21.5</v>
       </c>
       <c r="R7" t="n">
         <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U7" t="n">
-        <v>48.3</v>
+        <v>20.9</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -7547,134 +7547,134 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr"/>
@@ -7685,27 +7685,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -7715,26 +7715,26 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.4</v>
+        <v>43.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7752,22 +7752,22 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36.6</v>
+        <v>43.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>26.6</v>
+        <v>21.5</v>
       </c>
       <c r="R8" t="n">
         <v>27.6</v>
       </c>
       <c r="S8" t="n">
-        <v>95.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U8" t="n">
-        <v>65.2</v>
+        <v>0</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -7823,27 +7823,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -7853,104 +7853,104 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr"/>
       <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr"/>
@@ -7961,27 +7961,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Victor Mesa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -7991,26 +7991,26 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44</v>
+        <v>42.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,26 +8024,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>47.1</v>
+        <v>43.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.6</v>
+        <v>21.5</v>
       </c>
       <c r="R9" t="n">
         <v>27.6</v>
       </c>
       <c r="S9" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>13.3</v>
+        <v>54.9</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -8099,134 +8099,134 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr"/>
       <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr"/>
@@ -8237,27 +8237,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8267,17 +8267,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -8286,7 +8286,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>42.8</v>
+        <v>41.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,26 +8300,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>39.5</v>
+        <v>25.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>26.6</v>
+        <v>31.6</v>
       </c>
       <c r="R10" t="n">
         <v>27.6</v>
       </c>
       <c r="S10" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T10" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U10" t="n">
-        <v>37.8</v>
+        <v>23.4</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -8375,27 +8375,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -8405,104 +8405,104 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr"/>
       <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr"/>
@@ -8513,27 +8513,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8543,17 +8543,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -8562,7 +8562,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>42.1</v>
+        <v>40</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,26 +8576,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>32.7</v>
+        <v>32.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>36.5</v>
+        <v>31.6</v>
       </c>
       <c r="R11" t="n">
         <v>27.6</v>
       </c>
       <c r="S11" t="n">
-        <v>88.7</v>
+        <v>59.8</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U11" t="n">
-        <v>29.2</v>
+        <v>48.7</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -8651,134 +8651,134 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>99.7502</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr"/>
       <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr"/>
@@ -8789,27 +8789,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8819,17 +8819,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>41.1</v>
+        <v>36.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,26 +8852,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>36.4</v>
+        <v>20.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>36.5</v>
+        <v>33.4</v>
       </c>
       <c r="R12" t="n">
         <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T12" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -8927,134 +8927,134 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>99.6965</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4378</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -9065,27 +9065,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -9095,17 +9095,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -9114,7 +9114,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>40.3</v>
+        <v>34.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,26 +9128,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>35.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>36.5</v>
+        <v>33.4</v>
       </c>
       <c r="R13" t="n">
         <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>88.7</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>26.1</v>
+        <v>43.1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -9203,12 +9203,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -9218,119 +9218,119 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>100.9708</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3621</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>43.52</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.51</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1594</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr"/>
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr"/>
@@ -9341,27 +9341,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -9371,26 +9371,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>38.6</v>
+        <v>33.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,26 +9404,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>33.9</v>
+        <v>10.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>36.5</v>
+        <v>21.5</v>
       </c>
       <c r="R14" t="n">
         <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U14" t="n">
-        <v>12</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -9479,134 +9479,134 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.7109</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>27.96</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -9617,27 +9617,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>683734</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Andrew Vaughn</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -9647,17 +9647,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -9666,7 +9666,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>38.4</v>
+        <v>32.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,26 +9680,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>34.2</v>
+        <v>13.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>26.6</v>
+        <v>31.6</v>
       </c>
       <c r="R15" t="n">
         <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>81.90000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>13.6</v>
+        <v>72.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -9755,27 +9755,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9785,104 +9785,104 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>44.76</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>90.55</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>100.1817</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4097</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>70.53</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>12.73</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>33.72</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1437</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -9893,27 +9893,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>571771</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Enrique Hernandez</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -9942,7 +9942,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>35.2</v>
+        <v>30.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,26 +9956,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>32.6</v>
+        <v>7.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>36.5</v>
+        <v>33.4</v>
       </c>
       <c r="R16" t="n">
         <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>28.5</v>
+        <v>38.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -10036,129 +10036,129 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 1 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>39.49</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.9102</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3751</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1548</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2814</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.82</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1735</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr"/>
       <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -10169,27 +10169,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -10199,26 +10199,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.3</v>
+        <v>28.5</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10236,22 +10236,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>16.6</v>
+        <v>11.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>24.6</v>
+        <v>21.5</v>
       </c>
       <c r="R17" t="n">
         <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U17" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -10307,12 +10307,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -10322,12 +10322,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -10337,104 +10337,104 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -10445,27 +10445,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>663743</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -10475,26 +10475,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>28.1</v>
+        <v>27.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,26 +10508,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>10.5</v>
+        <v>12.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>26.6</v>
+        <v>21.5</v>
       </c>
       <c r="R18" t="n">
         <v>27.6</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U18" t="n">
-        <v>24.9</v>
+        <v>18.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -10583,27 +10583,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 2/17, 1 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10613,104 +10613,104 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.03</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>99.0812</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3248</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.093</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2721</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>72.49</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr"/>
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr"/>
@@ -10721,27 +10721,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00:00Z</t>
+          <t>2026-10-14T00:00:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -10751,26 +10751,26 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>27.4</v>
+        <v>25.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,26 +10784,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>17.1</v>
+        <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>26.6</v>
+        <v>20.1</v>
       </c>
       <c r="R19" t="n">
         <v>27.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T19" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>22.4</v>
+        <v>27</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -10874,12 +10874,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -10889,104 +10889,104 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>95.5424</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0794</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.35</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.0829</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr"/>
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr"/>
